--- a/themes/updatePassportData.xlsx
+++ b/themes/updatePassportData.xlsx
@@ -459,12 +459,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    isNotAuthorized: При смене паспорта нужно обновить информацию в банке. Вы можете актуализировать данные через «Уралсиб Онлайн» или в [веб-версии](https://online.uralsib.ru/), используя авторизацию через Госуслуги, либо в [офисе банка]({{$temp.officeLink}}).</t>
+          <t xml:space="preserve">    isNotAuthorized: При смене паспорта нужно обновить информацию в банке. Вы можете актуализировать данные через «Уралсиб Онлайн» или в [веб-версии](https://online.uralsib.ru/), используя авторизацию через Госуслуги, либо в [офисе банка]({{$temp.officeLink}})</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>убран лишний пробел перед запятой; добавлена точка в конце предложения</t>
+          <t>убран лишний пробел перед запятой</t>
         </is>
       </c>
     </row>
